--- a/excel/output_stats_vfvv/syrk/DVSInsertionData.xlsx
+++ b/excel/output_stats_vfvv/syrk/DVSInsertionData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,16 @@
           <t>voltage_level</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>voltage_value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>frequency_ghz</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -459,6 +469,12 @@
       </c>
       <c r="D2" t="n">
         <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -476,6 +492,12 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -492,6 +514,12 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -508,6 +536,12 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -524,6 +558,12 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
+      <c r="E6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -540,6 +580,12 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
+      <c r="E7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -556,6 +602,12 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
+      <c r="E8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -572,6 +624,12 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
+      <c r="E9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -588,6 +646,12 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
+      <c r="E10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -604,6 +668,12 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
+      <c r="E11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -620,6 +690,12 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
+      <c r="E12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -636,6 +712,12 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
+      <c r="E13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -652,6 +734,12 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
+      <c r="E14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -668,6 +756,12 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
+      <c r="E15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -684,6 +778,12 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
+      <c r="E16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -700,6 +800,12 @@
       <c r="D17" t="n">
         <v>0</v>
       </c>
+      <c r="E17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -716,6 +822,12 @@
       <c r="D18" t="n">
         <v>0</v>
       </c>
+      <c r="E18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -732,6 +844,12 @@
       <c r="D19" t="n">
         <v>0</v>
       </c>
+      <c r="E19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -748,6 +866,12 @@
       <c r="D20" t="n">
         <v>0</v>
       </c>
+      <c r="E20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -764,6 +888,12 @@
       <c r="D21" t="n">
         <v>0</v>
       </c>
+      <c r="E21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -780,6 +910,12 @@
       <c r="D22" t="n">
         <v>0</v>
       </c>
+      <c r="E22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -795,6 +931,12 @@
       </c>
       <c r="D23" t="n">
         <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
